--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty SDL Sep 2027 Index Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty SDL Sep 2027 Index Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="107">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty SDL Sep 2027 Index Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -178,51 +178,51 @@
     <t>IN2020170055</t>
   </si>
   <si>
+    <t>State Government of Telangana</t>
+  </si>
+  <si>
+    <t>IN4520190088</t>
+  </si>
+  <si>
     <t>IN1620170051</t>
   </si>
   <si>
+    <t>IN4520190104</t>
+  </si>
+  <si>
     <t>IN3120170060</t>
   </si>
   <si>
     <t>IN2920160438</t>
   </si>
   <si>
+    <t>IN3320170092</t>
+  </si>
+  <si>
+    <t>IN2120170039</t>
+  </si>
+  <si>
+    <t>IN3320170084</t>
+  </si>
+  <si>
     <t>State Government of Andhra Pradesh</t>
   </si>
   <si>
     <t>IN1020220100</t>
   </si>
   <si>
-    <t>IN3320170092</t>
-  </si>
-  <si>
-    <t>IN2120170039</t>
-  </si>
-  <si>
-    <t>IN3320170084</t>
-  </si>
-  <si>
     <t>IN2920170023</t>
   </si>
   <si>
-    <t>State Government of Telangana</t>
-  </si>
-  <si>
     <t>IN4520190062</t>
   </si>
   <si>
-    <t>IN4520190088</t>
-  </si>
-  <si>
     <t>State Government of Assam</t>
   </si>
   <si>
     <t>IN1220170030</t>
   </si>
   <si>
-    <t>IN4520190104</t>
-  </si>
-  <si>
     <t>IN1520170094</t>
   </si>
   <si>
@@ -319,19 +319,22 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
   </si>
   <si>
+    <t>Debt Index Replication Factor (DIRF) as on 31-5-2025</t>
+  </si>
+  <si>
+    <t>As per SEBI circular no. SEBI/HO/IMD/PoD/P/CIR/2024/183 dated December 31,2024, with respect to introduction of mutual Funds Lite (MF Lite) framework for passively managed schemes of Mutual Funds, Debt Index Replication Factor (DIRF) is disclosed for debt oriented passive schemes.</t>
+  </si>
+  <si>
     <t>Scheme Riskometer</t>
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - Nifty SDL Sep 2027 Index</t>
   </si>
 </sst>
 </file>
@@ -343,7 +346,7 @@
     <numFmt numFmtId="178" formatCode="##0.00%"/>
     <numFmt numFmtId="179" formatCode="##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -351,13 +354,21 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8.5"/>
-      <name val="Verdana"/>
+      <sz val="8.25"/>
+      <name val="Microsoft Sans Serif"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8.25"/>
-      <name val="Microsoft Sans Serif"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
@@ -531,37 +542,63 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
       <protection/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -572,51 +609,43 @@
       <alignment horizontal="right"/>
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
       <protection/>
     </xf>
   </cellXfs>
@@ -705,13 +734,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>103</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -729,7 +758,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="19697700"/>
+          <a:off x="666750" y="20231100"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -744,13 +773,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>116</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -768,7 +797,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="22555200"/>
+          <a:off x="666750" y="23088600"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1102,7 +1131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J115"/>
+  <dimension ref="B1:J116"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
@@ -1202,10 +1231,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>171408.05999999997</v>
+        <v>175379.09</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9719747333220997</v>
+        <v>0.9788490411700994</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1239,10 +1268,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>171408.05999999997</v>
+        <v>175379.09</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9719747333220997</v>
+        <v>0.9788490411700994</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1276,10 +1305,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>171408.05999999997</v>
+        <v>175379.09</v>
       </c>
       <c r="H9" s="10">
-        <v>0.9719747333220997</v>
+        <v>0.9788490411700994</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1305,13 +1334,13 @@
         <v>39897000</v>
       </c>
       <c r="G10" s="16">
-        <v>40192.68</v>
+        <v>40878.63</v>
       </c>
       <c r="H10" s="17">
-        <v>0.2279138415346</v>
+        <v>0.2281572323128</v>
       </c>
       <c r="I10" s="16">
-        <v>6.97</v>
+        <v>6.03</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>13</v>
@@ -1334,13 +1363,13 @@
         <v>20772870</v>
       </c>
       <c r="G11" s="16">
-        <v>20936.87</v>
+        <v>21300.19</v>
       </c>
       <c r="H11" s="17">
-        <v>0.1187231722645</v>
+        <v>0.1188834459016</v>
       </c>
       <c r="I11" s="16">
-        <v>6.97</v>
+        <v>6.03</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>13</v>
@@ -1363,13 +1392,13 @@
         <v>14000000</v>
       </c>
       <c r="G12" s="16">
-        <v>14121.17</v>
+        <v>14358.05</v>
       </c>
       <c r="H12" s="17">
-        <v>0.0800745335136</v>
+        <v>0.0801370532576</v>
       </c>
       <c r="I12" s="16">
-        <v>6.97</v>
+        <v>6.03</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>13</v>
@@ -1392,13 +1421,13 @@
         <v>10000000</v>
       </c>
       <c r="G13" s="16">
-        <v>10127.11</v>
+        <v>10316.39</v>
       </c>
       <c r="H13" s="17">
-        <v>0.0574260921079</v>
+        <v>0.0575792043388</v>
       </c>
       <c r="I13" s="16">
-        <v>7.03</v>
+        <v>6.05</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>13</v>
@@ -1421,13 +1450,13 @@
         <v>7500000</v>
       </c>
       <c r="G14" s="16">
-        <v>7604.61</v>
+        <v>7740.12</v>
       </c>
       <c r="H14" s="17">
-        <v>0.0431221774331</v>
+        <v>0.0432001844721</v>
       </c>
       <c r="I14" s="16">
-        <v>6.99</v>
+        <v>6.05</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>13</v>
@@ -1450,13 +1479,13 @@
         <v>7000000</v>
       </c>
       <c r="G15" s="16">
-        <v>7086.93</v>
+        <v>7214.82</v>
       </c>
       <c r="H15" s="17">
-        <v>0.0401866568984</v>
+        <v>0.040268310431</v>
       </c>
       <c r="I15" s="16">
-        <v>6.97</v>
+        <v>6.03</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>13</v>
@@ -1479,13 +1508,13 @@
         <v>6000000</v>
       </c>
       <c r="G16" s="16">
-        <v>5903</v>
+        <v>6022.67</v>
       </c>
       <c r="H16" s="17">
-        <v>0.0334731450248</v>
+        <v>0.0336145247121</v>
       </c>
       <c r="I16" s="16">
-        <v>6.96</v>
+        <v>6.01</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>13</v>
@@ -1508,13 +1537,13 @@
         <v>5197400</v>
       </c>
       <c r="G17" s="16">
-        <v>5243.50</v>
+        <v>5332.29</v>
       </c>
       <c r="H17" s="17">
-        <v>0.0297334297709</v>
+        <v>0.0297612842771</v>
       </c>
       <c r="I17" s="16">
-        <v>7.01</v>
+        <v>6.05</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>13</v>
@@ -1537,13 +1566,13 @@
         <v>4917000</v>
       </c>
       <c r="G18" s="16">
-        <v>5115.69</v>
+        <v>5188</v>
       </c>
       <c r="H18" s="17">
-        <v>0.0290086791923</v>
+        <v>0.028955953789</v>
       </c>
       <c r="I18" s="16">
-        <v>6.99</v>
+        <v>6.04</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>13</v>
@@ -1566,13 +1595,13 @@
         <v>4100000</v>
       </c>
       <c r="G19" s="16">
-        <v>4139.04</v>
+        <v>4211.66</v>
       </c>
       <c r="H19" s="17">
-        <v>0.0234705550031</v>
+        <v>0.0235066754693</v>
       </c>
       <c r="I19" s="16">
-        <v>6.99</v>
+        <v>6.05</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>13</v>
@@ -1595,13 +1624,13 @@
         <v>3700000</v>
       </c>
       <c r="G20" s="16">
-        <v>3749.45</v>
+        <v>3817.94</v>
       </c>
       <c r="H20" s="17">
-        <v>0.0212613727957</v>
+        <v>0.0213091931783</v>
       </c>
       <c r="I20" s="16">
-        <v>7.02</v>
+        <v>6.06</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>13</v>
@@ -1624,13 +1653,13 @@
         <v>3667000</v>
       </c>
       <c r="G21" s="16">
-        <v>3717.55</v>
+        <v>3784.97</v>
       </c>
       <c r="H21" s="17">
-        <v>0.021080482854</v>
+        <v>0.0211251766408</v>
       </c>
       <c r="I21" s="16">
-        <v>7.01</v>
+        <v>6.05</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>13</v>
@@ -1653,13 +1682,13 @@
         <v>3500000</v>
       </c>
       <c r="G22" s="16">
-        <v>3528.17</v>
+        <v>3588.90</v>
       </c>
       <c r="H22" s="17">
-        <v>0.0200065976761</v>
+        <v>0.0200308447481</v>
       </c>
       <c r="I22" s="16">
-        <v>7.01</v>
+        <v>6.08</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>13</v>
@@ -1682,13 +1711,13 @@
         <v>3310500</v>
       </c>
       <c r="G23" s="16">
-        <v>3257.25</v>
+        <v>3330.04</v>
       </c>
       <c r="H23" s="17">
-        <v>0.0184703373932</v>
+        <v>0.0185860609783</v>
       </c>
       <c r="I23" s="16">
-        <v>7.02</v>
+        <v>6.04</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>13</v>
@@ -1711,13 +1740,13 @@
         <v>3000000</v>
       </c>
       <c r="G24" s="16">
-        <v>3041.65</v>
+        <v>3078.20</v>
       </c>
       <c r="H24" s="17">
-        <v>0.0172477708902</v>
+        <v>0.0171804581637</v>
       </c>
       <c r="I24" s="16">
-        <v>6.96</v>
+        <v>6.04</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>13</v>
@@ -1740,13 +1769,13 @@
         <v>2599600</v>
       </c>
       <c r="G25" s="16">
-        <v>2624.03</v>
+        <v>2670</v>
       </c>
       <c r="H25" s="17">
-        <v>0.0148796436963</v>
+        <v>0.0149021581759</v>
       </c>
       <c r="I25" s="16">
-        <v>6.99</v>
+        <v>6.05</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>13</v>
@@ -1769,13 +1798,13 @@
         <v>2076160</v>
       </c>
       <c r="G26" s="16">
-        <v>2090.74</v>
+        <v>2126.83</v>
       </c>
       <c r="H26" s="17">
-        <v>0.0118556061713</v>
+        <v>0.0118705457203</v>
       </c>
       <c r="I26" s="16">
-        <v>6.97</v>
+        <v>6.03</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>13</v>
@@ -1798,13 +1827,13 @@
         <v>2000000</v>
       </c>
       <c r="G27" s="16">
-        <v>2025.21</v>
+        <v>2056.51</v>
       </c>
       <c r="H27" s="17">
-        <v>0.0114840162689</v>
+        <v>0.0114780664083</v>
       </c>
       <c r="I27" s="16">
-        <v>7.02</v>
+        <v>6.06</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>13</v>
@@ -1827,13 +1856,13 @@
         <v>1983000</v>
       </c>
       <c r="G28" s="16">
-        <v>2005.11</v>
+        <v>2040.79</v>
       </c>
       <c r="H28" s="17">
-        <v>0.011370038594</v>
+        <v>0.0113903278591</v>
       </c>
       <c r="I28" s="16">
-        <v>6.97</v>
+        <v>6.03</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>13</v>
@@ -1856,13 +1885,13 @@
         <v>1900000</v>
       </c>
       <c r="G29" s="16">
-        <v>1912.90</v>
+        <v>1946.35</v>
       </c>
       <c r="H29" s="17">
-        <v>0.0108471589222</v>
+        <v>0.0108632268036</v>
       </c>
       <c r="I29" s="16">
-        <v>7.01</v>
+        <v>6.05</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>13</v>
@@ -1885,13 +1914,13 @@
         <v>1766400</v>
       </c>
       <c r="G30" s="16">
-        <v>1791.48</v>
+        <v>1817.46</v>
       </c>
       <c r="H30" s="17">
-        <v>0.0101586430373</v>
+        <v>0.0101438488383</v>
       </c>
       <c r="I30" s="16">
-        <v>6.96</v>
+        <v>6.04</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>13</v>
@@ -1914,13 +1943,13 @@
         <v>1500000</v>
       </c>
       <c r="G31" s="16">
-        <v>1541.57</v>
+        <v>1560.12</v>
       </c>
       <c r="H31" s="17">
-        <v>0.0087415206125</v>
+        <v>0.0087075486941</v>
       </c>
       <c r="I31" s="16">
-        <v>7.03</v>
+        <v>6.07</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>13</v>
@@ -1943,13 +1972,13 @@
         <v>1500000</v>
       </c>
       <c r="G32" s="16">
-        <v>1521.19</v>
+        <v>1543.09</v>
       </c>
       <c r="H32" s="17">
-        <v>0.0086259551889</v>
+        <v>0.0086124985991</v>
       </c>
       <c r="I32" s="16">
-        <v>6.95</v>
+        <v>6.04</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>13</v>
@@ -1972,13 +2001,13 @@
         <v>1500000</v>
       </c>
       <c r="G33" s="16">
-        <v>1496.28</v>
+        <v>1518.92</v>
       </c>
       <c r="H33" s="17">
-        <v>0.0084847022595</v>
+        <v>0.0084775977889</v>
       </c>
       <c r="I33" s="16">
-        <v>6.96</v>
+        <v>6.06</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>13</v>
@@ -2001,13 +2030,13 @@
         <v>1395100</v>
       </c>
       <c r="G34" s="16">
-        <v>1406.18</v>
+        <v>1429.81</v>
       </c>
       <c r="H34" s="17">
-        <v>0.0079737874082</v>
+        <v>0.0079802452365</v>
       </c>
       <c r="I34" s="16">
-        <v>7.01</v>
+        <v>6.06</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>13</v>
@@ -2015,28 +2044,28 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D35" s="14">
-        <v>7.41</v>
+        <v>7.03</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="15">
-        <v>1167000</v>
+        <v>1333000</v>
       </c>
       <c r="G35" s="16">
-        <v>1181.76</v>
+        <v>1361.93</v>
       </c>
       <c r="H35" s="17">
-        <v>0.006701206821</v>
+        <v>0.0076013843762</v>
       </c>
       <c r="I35" s="16">
-        <v>6.99</v>
+        <v>6.06</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>13</v>
@@ -2044,28 +2073,28 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D36" s="14">
-        <v>7.27</v>
+        <v>7.41</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="15">
-        <v>1073320</v>
+        <v>1167000</v>
       </c>
       <c r="G36" s="16">
-        <v>1083.02</v>
+        <v>1203.05</v>
       </c>
       <c r="H36" s="17">
-        <v>0.0061412985812</v>
+        <v>0.0067146222447</v>
       </c>
       <c r="I36" s="16">
-        <v>6.98</v>
+        <v>6.05</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>13</v>
@@ -2073,28 +2102,28 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D37" s="14">
-        <v>7.85</v>
+        <v>7.38</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="15">
-        <v>1000000</v>
+        <v>1135000</v>
       </c>
       <c r="G37" s="16">
-        <v>1018.85</v>
+        <v>1168.89</v>
       </c>
       <c r="H37" s="17">
-        <v>0.0057774206011</v>
+        <v>0.0065239639214</v>
       </c>
       <c r="I37" s="16">
-        <v>6.99</v>
+        <v>6.06</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>13</v>
@@ -2102,28 +2131,28 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>58</v>
       </c>
       <c r="D38" s="14">
-        <v>7.46</v>
+        <v>7.27</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="15">
-        <v>1000000</v>
+        <v>1073320</v>
       </c>
       <c r="G38" s="16">
-        <v>1012.42</v>
+        <v>1101.19</v>
       </c>
       <c r="H38" s="17">
-        <v>0.0057409590862</v>
+        <v>0.006146107701</v>
       </c>
       <c r="I38" s="16">
-        <v>6.98</v>
+        <v>6.03</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>13</v>
@@ -2131,13 +2160,13 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>59</v>
       </c>
       <c r="D39" s="14">
-        <v>7.37</v>
+        <v>7.85</v>
       </c>
       <c r="E39" s="13" t="s">
         <v>18</v>
@@ -2146,13 +2175,13 @@
         <v>1000000</v>
       </c>
       <c r="G39" s="16">
-        <v>1011.27</v>
+        <v>1031.22</v>
       </c>
       <c r="H39" s="17">
-        <v>0.0057344379754</v>
+        <v>0.0057555818554</v>
       </c>
       <c r="I39" s="16">
-        <v>7.01</v>
+        <v>6.06</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>13</v>
@@ -2160,13 +2189,13 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C40" s="13" t="s">
         <v>60</v>
       </c>
       <c r="D40" s="14">
-        <v>7.35</v>
+        <v>7.37</v>
       </c>
       <c r="E40" s="13" t="s">
         <v>18</v>
@@ -2175,13 +2204,13 @@
         <v>1000000</v>
       </c>
       <c r="G40" s="16">
-        <v>1011.19</v>
+        <v>1029.55</v>
       </c>
       <c r="H40" s="17">
-        <v>0.005733984333</v>
+        <v>0.0057462610299</v>
       </c>
       <c r="I40" s="16">
-        <v>6.99</v>
+        <v>6.05</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>13</v>
@@ -2189,13 +2218,13 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D41" s="14">
-        <v>7.27</v>
+        <v>7.35</v>
       </c>
       <c r="E41" s="13" t="s">
         <v>18</v>
@@ -2204,13 +2233,13 @@
         <v>1000000</v>
       </c>
       <c r="G41" s="16">
-        <v>1008.78</v>
+        <v>1029.19</v>
       </c>
       <c r="H41" s="17">
-        <v>0.005720318353</v>
+        <v>0.0057442517502</v>
       </c>
       <c r="I41" s="16">
-        <v>7.01</v>
+        <v>6.05</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>13</v>
@@ -2218,13 +2247,13 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D42" s="14">
-        <v>7.23</v>
+        <v>7.27</v>
       </c>
       <c r="E42" s="13" t="s">
         <v>18</v>
@@ -2233,13 +2262,13 @@
         <v>1000000</v>
       </c>
       <c r="G42" s="16">
-        <v>1007</v>
+        <v>1026.82</v>
       </c>
       <c r="H42" s="17">
-        <v>0.0057102248077</v>
+        <v>0.0057310239918</v>
       </c>
       <c r="I42" s="16">
-        <v>7.02</v>
+        <v>6.05</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>13</v>
@@ -2253,7 +2282,7 @@
         <v>64</v>
       </c>
       <c r="D43" s="14">
-        <v>7.05</v>
+        <v>7.46</v>
       </c>
       <c r="E43" s="13" t="s">
         <v>18</v>
@@ -2262,13 +2291,13 @@
         <v>1000000</v>
       </c>
       <c r="G43" s="16">
-        <v>1003.55</v>
+        <v>1026.48</v>
       </c>
       <c r="H43" s="17">
-        <v>0.0056906614754</v>
+        <v>0.0057291263387</v>
       </c>
       <c r="I43" s="16">
-        <v>7.01</v>
+        <v>6.10</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>13</v>
@@ -2276,28 +2305,28 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>65</v>
       </c>
       <c r="D44" s="14">
-        <v>7.03</v>
+        <v>7.23</v>
       </c>
       <c r="E44" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="15">
-        <v>833000</v>
+        <v>1000000</v>
       </c>
       <c r="G44" s="16">
-        <v>835.63</v>
+        <v>1023.79</v>
       </c>
       <c r="H44" s="17">
-        <v>0.0047384658948</v>
+        <v>0.0057141125539</v>
       </c>
       <c r="I44" s="16">
-        <v>7.01</v>
+        <v>6.06</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>13</v>
@@ -2305,28 +2334,28 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>67</v>
-      </c>
       <c r="D45" s="14">
-        <v>7.29</v>
+        <v>7.05</v>
       </c>
       <c r="E45" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="15">
-        <v>700000</v>
+        <v>1000000</v>
       </c>
       <c r="G45" s="16">
-        <v>706.25</v>
+        <v>1021.26</v>
       </c>
       <c r="H45" s="17">
-        <v>0.0040048125823</v>
+        <v>0.0056999917823</v>
       </c>
       <c r="I45" s="16">
-        <v>7</v>
+        <v>6.06</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>13</v>
@@ -2334,28 +2363,28 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>68</v>
       </c>
       <c r="D46" s="14">
-        <v>7.38</v>
+        <v>7.29</v>
       </c>
       <c r="E46" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="15">
-        <v>635000</v>
+        <v>700000</v>
       </c>
       <c r="G46" s="16">
-        <v>642.32</v>
+        <v>717.19</v>
       </c>
       <c r="H46" s="17">
-        <v>0.0036422955297</v>
+        <v>0.0040028759633</v>
       </c>
       <c r="I46" s="16">
-        <v>7.01</v>
+        <v>6.10</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>13</v>
@@ -2378,13 +2407,13 @@
         <v>600000</v>
       </c>
       <c r="G47" s="16">
-        <v>605.41</v>
+        <v>616.10</v>
       </c>
       <c r="H47" s="17">
-        <v>0.0034329962272</v>
+        <v>0.0034386590457</v>
       </c>
       <c r="I47" s="16">
-        <v>6.97</v>
+        <v>6.03</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>13</v>
@@ -2407,13 +2436,13 @@
         <v>600000</v>
       </c>
       <c r="G48" s="16">
-        <v>604.87</v>
+        <v>614.56</v>
       </c>
       <c r="H48" s="17">
-        <v>0.0034299341404</v>
+        <v>0.0034300637934</v>
       </c>
       <c r="I48" s="16">
-        <v>6.97</v>
+        <v>6.03</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>13</v>
@@ -2436,13 +2465,13 @@
         <v>500000</v>
       </c>
       <c r="G49" s="16">
-        <v>504.01</v>
+        <v>512.79</v>
       </c>
       <c r="H49" s="17">
-        <v>0.0028580043747</v>
+        <v>0.0028620515696</v>
       </c>
       <c r="I49" s="16">
-        <v>6.97</v>
+        <v>6.03</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>13</v>
@@ -2465,13 +2494,13 @@
         <v>500000</v>
       </c>
       <c r="G50" s="16">
-        <v>503.98</v>
+        <v>512.79</v>
       </c>
       <c r="H50" s="17">
-        <v>0.0028578342587</v>
+        <v>0.0028620515696</v>
       </c>
       <c r="I50" s="16">
-        <v>6.98</v>
+        <v>6.03</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>13</v>
@@ -2494,13 +2523,13 @@
         <v>310100</v>
       </c>
       <c r="G51" s="16">
-        <v>312.56</v>
+        <v>317.99</v>
       </c>
       <c r="H51" s="17">
-        <v>0.0017723811975</v>
+        <v>0.0017748079694</v>
       </c>
       <c r="I51" s="16">
-        <v>6.99</v>
+        <v>6.05</v>
       </c>
       <c r="J51" s="11" t="s">
         <v>13</v>
@@ -2523,13 +2552,13 @@
         <v>200000</v>
       </c>
       <c r="G52" s="16">
-        <v>202.81</v>
+        <v>205.74</v>
       </c>
       <c r="H52" s="17">
-        <v>0.0011500404103</v>
+        <v>0.0011483033794</v>
       </c>
       <c r="I52" s="16">
-        <v>6.97</v>
+        <v>6.06</v>
       </c>
       <c r="J52" s="11" t="s">
         <v>13</v>
@@ -2552,13 +2581,13 @@
         <v>200000</v>
       </c>
       <c r="G53" s="16">
-        <v>201.34</v>
+        <v>203.87</v>
       </c>
       <c r="H53" s="17">
-        <v>0.0011417047296</v>
+        <v>0.0011378662873</v>
       </c>
       <c r="I53" s="16">
-        <v>6.95</v>
+        <v>6.03</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>13</v>
@@ -2581,13 +2610,13 @@
         <v>175000</v>
       </c>
       <c r="G54" s="16">
-        <v>177.52</v>
+        <v>179.86</v>
       </c>
       <c r="H54" s="17">
-        <v>0.0010066326791</v>
+        <v>0.0010038584904</v>
       </c>
       <c r="I54" s="16">
-        <v>6.99</v>
+        <v>6.06</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>13</v>
@@ -2595,7 +2624,7 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>77</v>
@@ -2610,13 +2639,13 @@
         <v>167000</v>
       </c>
       <c r="G55" s="16">
-        <v>173.12</v>
+        <v>175.44</v>
       </c>
       <c r="H55" s="17">
-        <v>0.0009816823423</v>
+        <v>0.0009791890001</v>
       </c>
       <c r="I55" s="16">
-        <v>7.02</v>
+        <v>6.11</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>13</v>
@@ -2639,13 +2668,13 @@
         <v>167000</v>
       </c>
       <c r="G56" s="16">
-        <v>169.32</v>
+        <v>171.83</v>
       </c>
       <c r="H56" s="17">
-        <v>0.0009601343241</v>
+        <v>0.0009590403892</v>
       </c>
       <c r="I56" s="16">
-        <v>6.97</v>
+        <v>6.04</v>
       </c>
       <c r="J56" s="11" t="s">
         <v>13</v>
@@ -2668,13 +2697,13 @@
         <v>150000</v>
       </c>
       <c r="G57" s="16">
-        <v>151.03</v>
+        <v>152.88</v>
       </c>
       <c r="H57" s="17">
-        <v>0.0008564203105</v>
+        <v>0.0008532741355</v>
       </c>
       <c r="I57" s="16">
-        <v>6.93</v>
+        <v>6.03</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>13</v>
@@ -2697,13 +2726,13 @@
         <v>100000</v>
       </c>
       <c r="G58" s="16">
-        <v>100.69</v>
+        <v>101.93</v>
       </c>
       <c r="H58" s="17">
-        <v>0.0005709657754</v>
+        <v>0.000568905237</v>
       </c>
       <c r="I58" s="16">
-        <v>6.94</v>
+        <v>6.03</v>
       </c>
       <c r="J58" s="11" t="s">
         <v>13</v>
@@ -3215,10 +3244,10 @@
         <v>13</v>
       </c>
       <c r="G86" s="9">
-        <v>2134.85</v>
+        <v>345.12</v>
       </c>
       <c r="H86" s="10">
-        <v>0.0121057332977</v>
+        <v>0.0019262295242</v>
       </c>
       <c r="I86" s="9" t="s">
         <v>13</v>
@@ -3252,10 +3281,10 @@
         <v>13</v>
       </c>
       <c r="G88" s="19">
-        <v>2807.4148831200146</v>
+        <v>3444.4693603000196</v>
       </c>
       <c r="H88" s="20">
-        <v>0.015919533377557936</v>
+        <v>0.019224729303124178</v>
       </c>
       <c r="I88" s="19" t="s">
         <v>13</v>
@@ -3281,10 +3310,10 @@
         <v>13</v>
       </c>
       <c r="G89" s="19">
-        <v>176350.32488312</v>
+        <v>179168.6793603</v>
       </c>
       <c r="H89" s="20">
-        <v>0.9999999999973577</v>
+        <v>0.9999999999974235</v>
       </c>
       <c r="I89" s="19" t="s">
         <v>13</v>
@@ -3349,23 +3378,41 @@
       <c r="G96" s="22"/>
       <c r="H96" s="22"/>
     </row>
-    <row r="99" ht="15">
-      <c r="B99" s="22" t="s">
+    <row r="97" spans="2:6" ht="15" customHeight="1">
+      <c r="B97" s="24" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="114" ht="15">
-      <c r="B114" s="22" t="s">
+      <c r="C97" s="25">
+        <v>0.9983727742280876</v>
+      </c>
+      <c r="D97" s="26"/>
+      <c r="E97" s="27"/>
+      <c r="F97" s="27"/>
+    </row>
+    <row r="98" spans="2:8" ht="27" customHeight="1">
+      <c r="B98" s="28" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="115" ht="15">
-      <c r="B115" s="22" t="s">
+      <c r="C98" s="29"/>
+      <c r="D98" s="29"/>
+      <c r="E98" s="29"/>
+      <c r="F98" s="29"/>
+      <c r="G98" s="29"/>
+      <c r="H98" s="29"/>
+    </row>
+    <row r="101" ht="15">
+      <c r="B101" s="22" t="s">
         <v>105</v>
       </c>
     </row>
+    <row r="116" ht="15">
+      <c r="B116" s="22" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="B98:H98"/>
     <mergeCell ref="B94:H94"/>
     <mergeCell ref="B95:H95"/>
     <mergeCell ref="B96:H96"/>
